--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487801_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487801_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. EFAMBE</t>
+          <t>S. ROMERO SANCHEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8584</v>
+        <v>6.0842</v>
       </c>
       <c r="E2" t="n">
-        <v>6.094</v>
+        <v>4.1982</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7644</v>
+        <v>1.886</v>
       </c>
       <c r="G2" t="n">
-        <v>3.448</v>
+        <v>5.0106</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3581</v>
+        <v>0.3031</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0899</v>
+        <v>4.7075</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5133</v>
+        <v>4.3087</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3174</v>
+        <v>0.1727</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1959</v>
+        <v>4.136</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9347</v>
+        <v>0.7019</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0407</v>
+        <v>0.1304</v>
       </c>
       <c r="O2" t="n">
-        <v>0.894</v>
+        <v>0.5715</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1211</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4132</v>
+        <v>-0.1105</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7079</v>
+        <v>0.0196</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.1675</v>
+        <v>0.1238</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.3351</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. ROMERO SANCHEZ</t>
+          <t>O. SIMA FATTY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9858</v>
+        <v>5.6806</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3054</v>
+        <v>3.372</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6805</v>
+        <v>2.3086</v>
       </c>
       <c r="G3" t="n">
-        <v>5.0106</v>
+        <v>3.8478</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3031</v>
+        <v>1.1324</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7075</v>
+        <v>2.7154</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3087</v>
+        <v>3.3581</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1727</v>
+        <v>1.5734</v>
       </c>
       <c r="L3" t="n">
-        <v>4.136</v>
+        <v>1.7847</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7019</v>
+        <v>0.4897</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1304</v>
+        <v>-0.4411</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5715</v>
+        <v>0.9307</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0406</v>
+        <v>1.2487</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0406</v>
+        <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1892</v>
+        <v>0.5841</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0033</v>
+        <v>0.222</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1859</v>
+        <v>0.3621</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. SIMA FATTY</t>
+          <t>D. EFAMBE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9034</v>
+        <v>4.7981</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7709</v>
+        <v>4.4448</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1325</v>
+        <v>0.3534</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8478</v>
+        <v>3.448</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1324</v>
+        <v>2.3581</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7154</v>
+        <v>1.0899</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3581</v>
+        <v>2.5133</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5734</v>
+        <v>2.3174</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7847</v>
+        <v>0.1959</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4897</v>
+        <v>0.9347</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4411</v>
+        <v>0.0407</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9307</v>
+        <v>0.894</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>1.4568</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1931</v>
+        <v>1.0608</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3791</v>
+        <v>0.7639</v>
       </c>
       <c r="U4" t="n">
-        <v>0.186</v>
+        <v>0.2969</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.4913</v>
+        <v>3.885</v>
       </c>
       <c r="E5" t="n">
-        <v>2.798</v>
+        <v>2.6908</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6933</v>
+        <v>1.1942</v>
       </c>
       <c r="G5" t="n">
         <v>3.1928</v>
@@ -844,13 +844,13 @@
         <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8416</v>
+        <v>0.2354</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.1757</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9102</v>
+        <v>0.4111</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5838</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0367</v>
+        <v>2.6209</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2143</v>
+        <v>0.4286</v>
       </c>
       <c r="F6" t="n">
-        <v>2.251</v>
+        <v>2.1923</v>
       </c>
       <c r="G6" t="n">
         <v>3.741</v>
@@ -922,13 +922,13 @@
         <v>2.2893</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7907</v>
+        <v>-0.2065</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9786</v>
+        <v>-0.3357</v>
       </c>
       <c r="U6" t="n">
-        <v>0.188</v>
+        <v>0.1292</v>
       </c>
       <c r="V6" t="n">
         <v>1.1675</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1894</v>
+        <v>1.7523</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3504</v>
+        <v>0.0363</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5399</v>
+        <v>1.716</v>
       </c>
       <c r="G7" t="n">
         <v>0.0633</v>
@@ -1000,13 +1000,13 @@
         <v>1.0406</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1683</v>
+        <v>0.3946</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2486</v>
+        <v>0.1381</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0803</v>
+        <v>0.2564</v>
       </c>
       <c r="V7" t="n">
         <v>2.3351</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. TREVIÑO QUINTILLÁ</t>
+          <t>R. BLAK MOLLER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7538</v>
+        <v>1.0224</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0383</v>
+        <v>-0.9132</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7155</v>
+        <v>1.9356</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1347</v>
+        <v>-0.8701</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0106</v>
+        <v>-0.377</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1453</v>
+        <v>-0.4931</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4983</v>
+        <v>-1.0699</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3897</v>
+        <v>0.2111</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1086</v>
+        <v>-1.281</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3636</v>
+        <v>0.1998</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4004</v>
+        <v>-0.5881</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0367</v>
+        <v>0.7879</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.4575</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5806</v>
+        <v>0.1567</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0823</v>
+        <v>0.3008</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4599</v>
+        <v>-0.23</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4599</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4186</v>
+        <v>0.8068</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0175</v>
+        <v>-0.9523</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4361</v>
+        <v>1.759</v>
       </c>
       <c r="G9" t="n">
         <v>1.3599</v>
@@ -1156,13 +1156,13 @@
         <v>1.4568</v>
       </c>
       <c r="S9" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.4854</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2048</v>
+        <v>0.2701</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1076</v>
+        <v>0.2153</v>
       </c>
       <c r="V9" t="n">
         <v>1.8751</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. BLAK MOLLER</t>
+          <t>P. TREVIÑO QUINTILLÁ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.392</v>
+        <v>0.0522</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5142</v>
+        <v>-0.6046</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9062</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8701</v>
+        <v>0.1347</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.377</v>
+        <v>-0.0106</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4931</v>
+        <v>0.1453</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0699</v>
+        <v>0.4983</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2111</v>
+        <v>0.3897</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.281</v>
+        <v>0.1086</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1998</v>
+        <v>-0.3636</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5881</v>
+        <v>-0.4004</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7879</v>
+        <v>0.0367</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1729</v>
+        <v>-0.0388</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4443</v>
+        <v>-0.0624</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2715</v>
+        <v>0.0235</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.23</v>
+        <v>-0.4599</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.23</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8025</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="E11" t="n">
         <v>-1.0014</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1989</v>
+        <v>0.0815</v>
       </c>
       <c r="G11" t="n">
         <v>0.1331</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.105</v>
+        <v>-0.0124</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.105</v>
+        <v>-0.0124</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6942</v>
+        <v>-0.9235</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1538</v>
+        <v>-0.618</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5404</v>
+        <v>-0.3055</v>
       </c>
       <c r="G12" t="n">
         <v>1.6555</v>
@@ -1390,13 +1390,13 @@
         <v>1.4568</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7659</v>
+        <v>0.0047</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7829</v>
+        <v>-0.2471</v>
       </c>
       <c r="U12" t="n">
-        <v>0.017</v>
+        <v>0.2519</v>
       </c>
       <c r="V12" t="n">
         <v>-1.7513</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>24.5327</v>
+        <v>24.8591</v>
       </c>
       <c r="E13" t="n">
-        <v>10.755</v>
+        <v>11.0812</v>
       </c>
       <c r="F13" t="n">
         <v>13.7779</v>
@@ -1444,7 +1444,7 @@
         <v>20.1267</v>
       </c>
       <c r="K13" t="n">
-        <v>6.0844</v>
+        <v>6.084400000000001</v>
       </c>
       <c r="L13" t="n">
         <v>14.0424</v>
@@ -1468,13 +1468,13 @@
         <v>14.5681</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5476</v>
+        <v>2.874</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2932999999999998</v>
+        <v>0.6194000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2547</v>
+        <v>2.2544</v>
       </c>
       <c r="V13" t="n">
         <v>1.309</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. MARTIN MARTIN</t>
+          <t>P. MARIN FONTAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5016</v>
+        <v>0.379</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7228</v>
+        <v>1.6782</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2212</v>
+        <v>-1.2993</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.2928</v>
+        <v>-1.3424</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3923</v>
+        <v>1.5436</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.6851</v>
+        <v>-2.886</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2138</v>
+        <v>0.6008</v>
       </c>
       <c r="K14" t="n">
-        <v>1.262</v>
+        <v>2.0295</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0482</v>
+        <v>-1.4287</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.5066</v>
+        <v>-1.9432</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8697</v>
+        <v>-0.4859</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.6369</v>
+        <v>-1.4573</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.2487</v>
+        <v>-0.2081</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0812</v>
+        <v>0.4162</v>
       </c>
       <c r="S14" t="n">
-        <v>0.732</v>
+        <v>-0.1142</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5276999999999999</v>
+        <v>-0.3419</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2042</v>
+        <v>0.2277</v>
       </c>
       <c r="V14" t="n">
-        <v>0.23</v>
+        <v>1.6275</v>
       </c>
       <c r="W14" t="n">
-        <v>0.23</v>
+        <v>1.6275</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. MARIN FONTAN</t>
+          <t>P. MARTIN MARTIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0457</v>
+        <v>0.0436</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2496</v>
+        <v>0.2942</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2953</v>
+        <v>-0.2506</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.3424</v>
+        <v>-1.2928</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5436</v>
+        <v>0.3923</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.886</v>
+        <v>-1.6851</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6008</v>
+        <v>1.2138</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0295</v>
+        <v>1.262</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4287</v>
+        <v>-0.0482</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9432</v>
+        <v>-2.5066</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4859</v>
+        <v>-0.8697</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4573</v>
+        <v>-1.6369</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2081</v>
+        <v>-1.2487</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4162</v>
+        <v>2.0812</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5389</v>
+        <v>0.274</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7705</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2317</v>
+        <v>0.1749</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6275</v>
+        <v>0.23</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6275</v>
+        <v>0.23</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9039</v>
+        <v>-0.0364</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.742</v>
+        <v>0.0081</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1619</v>
+        <v>-0.0444</v>
       </c>
       <c r="G16" t="n">
         <v>1.009</v>
@@ -1702,13 +1702,13 @@
         <v>3.1218</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4966</v>
+        <v>-0.6291</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3701</v>
+        <v>-0.62</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1265</v>
+        <v>-0.0091</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5844</v>
+        <v>-1.0334</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6782</v>
+        <v>1.3211</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2625</v>
+        <v>-2.3546</v>
       </c>
       <c r="G17" t="n">
         <v>-2.083</v>
@@ -1780,13 +1780,13 @@
         <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1039</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1744</v>
+        <v>-0.5314</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07049999999999999</v>
+        <v>-0.0215</v>
       </c>
       <c r="V17" t="n">
         <v>0.3538</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4</v>
+        <v>-2.7699</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1385</v>
+        <v>-1.5671</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2615</v>
+        <v>-1.2028</v>
       </c>
       <c r="G18" t="n">
         <v>-2.8584</v>
@@ -1858,13 +1858,13 @@
         <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4397</v>
+        <v>0.0698</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6458</v>
+        <v>0.2172</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2061</v>
+        <v>-0.1474</v>
       </c>
       <c r="V18" t="n">
         <v>-0.8137</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.7159</v>
+        <v>-3.0754</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1955</v>
+        <v>-1.8741</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5204</v>
+        <v>-1.2013</v>
       </c>
       <c r="G19" t="n">
         <v>-1.426</v>
@@ -1936,13 +1936,13 @@
         <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8331</v>
+        <v>-0.1926</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7705</v>
+        <v>-0.4491</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0626</v>
+        <v>0.2564</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0103</v>
+        <v>-4.1747</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7201</v>
+        <v>-3.1488</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2902</v>
+        <v>-1.0259</v>
       </c>
       <c r="G20" t="n">
         <v>-4.1955</v>
@@ -2014,13 +2014,13 @@
         <v>1.8731</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.231</v>
+        <v>-0.3954</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4501</v>
+        <v>0.0215</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6811</v>
+        <v>-0.4169</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.5295</v>
+        <v>-5.4659</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.7022</v>
+        <v>-4.4879</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8273</v>
+        <v>-0.978</v>
       </c>
       <c r="G21" t="n">
         <v>-5.5115</v>
@@ -2092,13 +2092,13 @@
         <v>2.2893</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.351</v>
+        <v>-0.2874</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7086</v>
+        <v>-0.4943</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3576</v>
+        <v>0.2069</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7076</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.8447</v>
+        <v>-7.6853</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.9301</v>
+        <v>-6.0017</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9146</v>
+        <v>-1.6836</v>
       </c>
       <c r="G22" t="n">
         <v>-4.0158</v>
@@ -2170,13 +2170,13 @@
         <v>1.6649</v>
       </c>
       <c r="S22" t="n">
-        <v>0.835</v>
+        <v>-0.0056</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9159</v>
+        <v>-0.1557</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0809</v>
+        <v>0.1501</v>
       </c>
       <c r="V22" t="n">
         <v>-1.999</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-24.5328</v>
+        <v>-23.8184</v>
       </c>
       <c r="E23" t="n">
-        <v>-13.7778</v>
+        <v>-13.778</v>
       </c>
       <c r="F23" t="n">
-        <v>-10.7549</v>
+        <v>-10.0405</v>
       </c>
       <c r="G23" t="n">
         <v>-21.7164</v>
@@ -2248,13 +2248,13 @@
         <v>15.6089</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.547800000000001</v>
+        <v>-1.8334</v>
       </c>
       <c r="T23" t="n">
         <v>-2.2546</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2932000000000001</v>
+        <v>0.4211</v>
       </c>
       <c r="V23" t="n">
         <v>-1.309</v>
